--- a/ig/DM-SIDOBA/CodeSystem-TRE-R286-TypeFermeture.xlsx
+++ b/ig/DM-SIDOBA/CodeSystem-TRE-R286-TypeFermeture.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="85">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251016120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-16T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -97,6 +97,9 @@
     <t>Value Set (all codes)</t>
   </si>
   <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R286-TypeFermeture/FHIR/TRE-R286-TypeFermeture?vs</t>
+  </si>
+  <si>
     <t>Hierarchy</t>
   </si>
   <si>
@@ -133,6 +136,9 @@
     <t>dateValid</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
     <t>date de validité d'un code concept</t>
   </si>
   <si>
@@ -142,34 +148,40 @@
     <t>dateMaj</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
     <t>Date de mise à jour d'un code concept</t>
   </si>
   <si>
     <t>dateFin</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
     <t>Date de fin d'exploitation d'un code concept</t>
   </si>
   <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>Statut d'un code concept</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
     <t>deprecationDate</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
   </si>
   <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>code</t>
+    <t>Date de dépréciation du code</t>
   </si>
   <si>
     <t>retirementDate</t>
@@ -178,7 +190,28 @@
     <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
   </si>
   <si>
-    <t>Date Concept was retired</t>
+    <t>Date de retrait du code</t>
+  </si>
+  <si>
+    <t>TypeFermeturePmFiness</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#TypeFermeturePmFiness</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes à inclure dans le JdvJ364TypeFermeturePmFiness</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>TypeFermetureEgeFiness</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#TypeFermetureEgeFiness</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes à inclure dans le JdvJ365TypeFermetureEgeFiness</t>
   </si>
   <si>
     <t>Level</t>
@@ -199,9 +232,6 @@
     <t>Définitive</t>
   </si>
   <si>
-    <t>Désigne la fermeture définitive d’un élément de l’organisation interne d’un établissement de santé</t>
-  </si>
-  <si>
     <t>ERR</t>
   </si>
   <si>
@@ -230,9 +260,6 @@
   </si>
   <si>
     <t>Provisoire</t>
-  </si>
-  <si>
-    <t>Désigne la fermeture provisoire d’un élément de l’organisation interne d’un établissement santé. L’utilisateur du référentiel ROR qui sélectionne cette valeur doit alors obligatoirement renseigner une date de réouverture de l’élément en question.</t>
   </si>
   <si>
     <t>PRE</t>
@@ -500,46 +527,48 @@
       <c r="A16" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" t="s" s="2">
+        <v>27</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -549,99 +578,133 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>21</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="C2" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>44</v>
+      </c>
       <c r="C3" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>47</v>
+      </c>
       <c r="C4" t="s" s="2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -656,106 +719,102 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>61</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
